--- a/docs/data/beidan_26081_dashboard.xlsx
+++ b/docs/data/beidan_26081_dashboard.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26081期 比赛看板（皇冠历史相同亚盘） — 2026-07-31</t>
+          <t>⚽ 北京单场26081期 比赛看板（皇冠历史相同亚盘） — 2026-08-01</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>08-01 07:30</t>
+          <t>08-01 07:40</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>08-01 11:00</t>
+          <t>08-01 11:10</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -3580,7 +3580,11 @@
           <t>邓弗姆林</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
           <t>32%</t>
@@ -3588,12 +3592,12 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>44%</t>
         </is>
       </c>
     </row>
@@ -3626,20 +3630,24 @@
           <t>女王公园</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>一球</t>
+        </is>
+      </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -3672,20 +3680,24 @@
           <t>斯坦豪斯摩尔</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>一球</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6312,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>08-02 10:30</t>
+          <t>08-02 10:45</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -9118,20 +9130,24 @@
           <t>福塔雷萨</t>
         </is>
       </c>
-      <c r="G174" s="4" t="inlineStr"/>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>球半/两球</t>
+        </is>
+      </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -9164,20 +9180,24 @@
           <t>博卡青年</t>
         </is>
       </c>
-      <c r="G175" s="5" t="inlineStr"/>
-      <c r="H175" s="7" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="I175" s="7" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="J175" s="5" t="inlineStr">
-        <is>
-          <t>16%</t>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>受半球</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="J175" s="8" t="inlineStr">
+        <is>
+          <t>55%</t>
         </is>
       </c>
     </row>
@@ -9210,20 +9230,24 @@
           <t>格雷米奥</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr"/>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>17%</t>
         </is>
       </c>
     </row>
@@ -9356,20 +9380,24 @@
           <t>科林蒂安</t>
         </is>
       </c>
-      <c r="G179" s="5" t="inlineStr"/>
-      <c r="H179" s="7" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="I179" s="5" t="inlineStr">
-        <is>
-          <t>31%</t>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
+      <c r="H179" s="8" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="I179" s="7" t="inlineStr">
+        <is>
+          <t>37%</t>
         </is>
       </c>
       <c r="J179" s="5" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>17%</t>
         </is>
       </c>
     </row>
@@ -10378,20 +10406,24 @@
           <t>门多萨独立</t>
         </is>
       </c>
-      <c r="G200" s="4" t="inlineStr"/>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
@@ -10424,20 +10456,24 @@
           <t>阿根廷独立</t>
         </is>
       </c>
-      <c r="G201" s="5" t="inlineStr"/>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I201" s="7" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="J201" s="5" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>24%</t>
         </is>
       </c>
     </row>
@@ -10470,20 +10506,24 @@
           <t>塔勒瑞斯</t>
         </is>
       </c>
-      <c r="G202" s="4" t="inlineStr"/>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -10516,20 +10556,24 @@
           <t>维多利亚</t>
         </is>
       </c>
-      <c r="G203" s="5" t="inlineStr"/>
-      <c r="H203" s="7" t="inlineStr">
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>半球/一球</t>
+        </is>
+      </c>
+      <c r="H203" s="8" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="I203" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="I203" s="5" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
       <c r="J203" s="5" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>16%</t>
         </is>
       </c>
     </row>
@@ -10562,20 +10606,24 @@
           <t>圣洛伦索</t>
         </is>
       </c>
-      <c r="G204" s="4" t="inlineStr"/>
+      <c r="G204" s="4" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -10608,20 +10656,24 @@
           <t>图库曼竞技</t>
         </is>
       </c>
-      <c r="G205" s="5" t="inlineStr"/>
-      <c r="H205" s="7" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="I205" s="7" t="inlineStr">
-        <is>
-          <t>38%</t>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
+      <c r="H205" s="8" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
+          <t>29%</t>
         </is>
       </c>
       <c r="J205" s="5" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>22%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26081_dashboard.xlsx
+++ b/docs/data/beidan_26081_dashboard.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26081期 比赛看板（皇冠历史相同亚盘） — 2026-08-01</t>
+          <t>⚽ 北京单场26081期 比赛看板（皇冠历史相同亚盘） — 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>08-02 07:30</t>
+          <t>08-02 09:40</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>08-02 07:30</t>
+          <t>08-02 07:40</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>08-02 07:30</t>
+          <t>08-02 08:10</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>08-02 07:30</t>
+          <t>08-02 07:40</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>08-02 07:30</t>
+          <t>08-02 07:40</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>08-02 07:30</t>
+          <t>08-02 07:40</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>08-02 07:30</t>
+          <t>08-02 07:40</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>08-02 08:30</t>
+          <t>08-02 08:40</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>08-02 08:30</t>
+          <t>08-02 08:40</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>08-02 08:30</t>
+          <t>08-02 08:40</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>08-02 09:30</t>
+          <t>08-02 09:40</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>08-02 10:30</t>
+          <t>08-02 10:40</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>08-02 10:45</t>
+          <t>08-02 10:50</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>08-03 09:05</t>
+          <t>08-03 09:10</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -10060,10 +10060,14 @@
           <t>什切青波贡</t>
         </is>
       </c>
-      <c r="G193" s="5" t="inlineStr"/>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="I193" s="5" t="inlineStr">
@@ -10073,7 +10077,7 @@
       </c>
       <c r="J193" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26081_dashboard.xlsx
+++ b/docs/data/beidan_26081_dashboard.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26081期 比赛看板（皇冠历史相同亚盘） — 2026-08-02</t>
+          <t>⚽ 北京单场26081期 比赛看板（皇冠历史相同亚盘） — 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>08-02 23:00</t>
+          <t>08-02 23:15</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -9680,20 +9680,24 @@
           <t>条约联</t>
         </is>
       </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
-        <is>
-          <t>34%</t>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>半球/一球</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="inlineStr">
+        <is>
+          <t>39%</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="J185" s="7" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>39%</t>
         </is>
       </c>
     </row>
@@ -9726,10 +9730,14 @@
           <t>布雷流浪者</t>
         </is>
       </c>
-      <c r="G186" s="4" t="inlineStr"/>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
@@ -9739,7 +9747,7 @@
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>46%</t>
         </is>
       </c>
     </row>
@@ -9772,20 +9780,24 @@
           <t>费恩夏普</t>
         </is>
       </c>
-      <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
-        <is>
-          <t>34%</t>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>半球/一球</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr">
+        <is>
+          <t>39%</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="J187" s="7" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>39%</t>
         </is>
       </c>
     </row>
@@ -9818,15 +9830,19 @@
           <t>科布漫步者</t>
         </is>
       </c>
-      <c r="G188" s="4" t="inlineStr"/>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="J188" s="4" t="inlineStr">
@@ -9864,20 +9880,24 @@
           <t>阿斯隆城</t>
         </is>
       </c>
-      <c r="G189" s="5" t="inlineStr"/>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>一球/球半</t>
+        </is>
+      </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="I189" s="5" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="J189" s="7" t="inlineStr">
-        <is>
-          <t>38%</t>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="I189" s="8" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>15%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26081_dashboard.xlsx
+++ b/docs/data/beidan_26081_dashboard.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J213"/>
+  <dimension ref="A1:L213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -529,10 +529,12 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,20 +584,30 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>比分</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>赛果</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>亚盘(胜负过关)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>皇冠历史概率% (主胜)</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>皇冠历史概率% (平)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>皇冠历史概率% (客胜)</t>
         </is>
@@ -632,20 +644,30 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -682,20 +704,30 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
           <t>球半</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -732,20 +764,30 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -782,20 +824,30 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -832,20 +884,30 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -882,20 +944,30 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -932,20 +1004,30 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -982,20 +1064,30 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -1032,20 +1124,30 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -1082,20 +1184,30 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -1132,20 +1244,30 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -1182,20 +1304,30 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
           <t>球半/两球</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -1232,20 +1364,30 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -1282,20 +1424,30 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
@@ -1332,20 +1484,30 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -1382,20 +1544,30 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1432,20 +1604,30 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -1482,20 +1664,30 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1532,20 +1724,30 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -1582,20 +1784,30 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1632,20 +1844,30 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1682,20 +1904,30 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1732,20 +1964,30 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -1782,20 +2024,30 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -1832,20 +2084,30 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -1882,20 +2144,30 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -1932,20 +2204,30 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
@@ -1982,20 +2264,30 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -2032,20 +2324,30 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
           <t>受球半</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -2082,20 +2384,30 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -2132,20 +2444,30 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2182,20 +2504,30 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
           <t>受一球</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -2232,20 +2564,30 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
           <t>球半</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -2282,20 +2624,30 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -2332,20 +2684,30 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -2382,20 +2744,30 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -2432,20 +2804,30 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -2482,20 +2864,30 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -2532,20 +2924,30 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
+          <t>1:5</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -2582,20 +2984,30 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -2632,20 +3044,30 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -2682,20 +3104,30 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -2732,20 +3164,30 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -2782,20 +3224,30 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -2832,20 +3284,30 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
           <t>受一球</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2882,20 +3344,30 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -2932,20 +3404,30 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -2982,20 +3464,30 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3032,20 +3524,30 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -3082,20 +3584,30 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -3132,20 +3644,30 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="L54" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -3182,20 +3704,30 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3232,20 +3764,30 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="L56" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3282,20 +3824,30 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J57" s="7" t="inlineStr">
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
@@ -3332,20 +3884,30 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="K58" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="L58" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -3382,20 +3944,30 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="J59" s="7" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -3432,20 +4004,30 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="K60" s="4" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="L60" s="4" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -3482,20 +4064,30 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="J61" s="7" t="inlineStr">
+      <c r="L61" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -3532,20 +4124,30 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -3582,20 +4184,30 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="K63" s="5" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="J63" s="7" t="inlineStr">
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -3632,20 +4244,30 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="K64" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="L64" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -3682,20 +4304,30 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="J65" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
+      <c r="L65" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -3732,20 +4364,30 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="K66" s="4" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="L66" s="4" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -3782,20 +4424,30 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr">
+      <c r="J67" s="8" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="K67" s="5" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="L67" s="5" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -3832,20 +4484,30 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="K68" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -3882,20 +4544,30 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr">
+      <c r="J69" s="8" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -3932,20 +4604,30 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="K70" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="L70" s="4" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
@@ -3982,20 +4664,30 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="J71" s="7" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J71" s="7" t="inlineStr">
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -4032,20 +4724,30 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr">
+      <c r="K72" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="L72" s="4" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -4082,20 +4784,30 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="K73" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4132,20 +4844,30 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="K74" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="L74" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4182,20 +4904,30 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="K75" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="J75" s="7" t="inlineStr">
+      <c r="L75" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -4232,20 +4964,30 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="L76" s="4" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -4282,20 +5024,30 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="K77" s="5" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="J77" s="8" t="inlineStr">
+      <c r="L77" s="8" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -4332,20 +5084,30 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -4382,20 +5144,30 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
           <t>受一球</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="K79" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J79" s="5" t="inlineStr">
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -4432,20 +5204,30 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="L80" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -4482,20 +5264,30 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="J81" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -4532,20 +5324,30 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J82" s="4" t="inlineStr">
+      <c r="L82" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4582,20 +5384,30 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr">
+      <c r="J83" s="8" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="K83" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="L83" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -4632,20 +5444,30 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J84" s="4" t="inlineStr">
+      <c r="L84" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -4682,20 +5504,30 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="J85" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="K85" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="L85" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -4732,20 +5564,30 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
           <t>球半</t>
         </is>
       </c>
-      <c r="H86" s="4" t="inlineStr">
+      <c r="J86" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr">
+      <c r="K86" s="4" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="J86" s="4" t="inlineStr">
+      <c r="L86" s="4" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -4782,20 +5624,30 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
           <t>球半</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="J87" s="8" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="K87" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J87" s="5" t="inlineStr">
+      <c r="L87" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4832,20 +5684,30 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
+          <t>0:6</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
+      <c r="J88" s="4" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr">
+      <c r="K88" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="L88" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -4882,20 +5744,30 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="K89" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J89" s="8" t="inlineStr">
+      <c r="L89" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -4932,20 +5804,30 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="J90" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr">
+      <c r="K90" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="L90" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -4982,20 +5864,30 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H91" s="7" t="inlineStr">
+      <c r="J91" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="K91" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J91" s="5" t="inlineStr">
+      <c r="L91" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -5032,20 +5924,30 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr">
+      <c r="J92" s="4" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr">
+      <c r="K92" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J92" s="4" t="inlineStr">
+      <c r="L92" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5082,20 +5984,30 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
           <t>两球半/三球</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="K93" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J93" s="5" t="inlineStr">
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5132,20 +6044,30 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr">
+      <c r="J94" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr">
+      <c r="K94" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="L94" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -5182,20 +6104,30 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="K95" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J95" s="8" t="inlineStr">
+      <c r="L95" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -5232,20 +6164,30 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H96" s="4" t="inlineStr">
+      <c r="J96" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I96" s="4" t="inlineStr">
+      <c r="K96" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J96" s="4" t="inlineStr">
+      <c r="L96" s="4" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -5282,20 +6224,30 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="J97" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="K97" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -5332,20 +6284,30 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
+      <c r="J98" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I98" s="4" t="inlineStr">
+      <c r="K98" s="4" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="J98" s="4" t="inlineStr">
+      <c r="L98" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -5382,20 +6344,30 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="J99" s="5" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr">
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="J99" s="8" t="inlineStr">
+      <c r="L99" s="8" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -5432,20 +6404,30 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr">
+      <c r="J100" s="4" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="I100" s="4" t="inlineStr">
+      <c r="K100" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J100" s="4" t="inlineStr">
+      <c r="L100" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -5482,20 +6464,30 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
+      <c r="J101" s="8" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="K101" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J101" s="5" t="inlineStr">
+      <c r="L101" s="5" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -5532,20 +6524,30 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr">
+      <c r="J102" s="4" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
       </c>
-      <c r="I102" s="4" t="inlineStr">
+      <c r="K102" s="4" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J102" s="4" t="inlineStr">
+      <c r="L102" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5582,20 +6584,30 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="J103" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="K103" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J103" s="7" t="inlineStr">
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -5632,20 +6644,30 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
+      <c r="J104" s="4" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="I104" s="4" t="inlineStr">
+      <c r="K104" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr">
+      <c r="L104" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -5682,20 +6704,30 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H105" s="8" t="inlineStr">
+      <c r="J105" s="8" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="K105" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J105" s="5" t="inlineStr">
+      <c r="L105" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -5732,20 +6764,30 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr">
+      <c r="J106" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I106" s="4" t="inlineStr">
+      <c r="K106" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J106" s="4" t="inlineStr">
+      <c r="L106" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -5782,20 +6824,30 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="J107" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="K107" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J107" s="7" t="inlineStr">
+      <c r="L107" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -5832,20 +6884,30 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>＊</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr">
+      <c r="J108" s="4" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="I108" s="4" t="inlineStr">
+      <c r="K108" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J108" s="4" t="inlineStr">
+      <c r="L108" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -5882,20 +6944,30 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H109" s="8" t="inlineStr">
+      <c r="J109" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I109" s="7" t="inlineStr">
+      <c r="K109" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="J109" s="5" t="inlineStr">
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -5932,20 +7004,30 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr">
+      <c r="J110" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I110" s="4" t="inlineStr">
+      <c r="K110" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J110" s="4" t="inlineStr">
+      <c r="L110" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -5982,20 +7064,30 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H111" s="8" t="inlineStr">
+      <c r="J111" s="8" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="K111" s="5" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J111" s="5" t="inlineStr">
+      <c r="L111" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -6032,20 +7124,30 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H112" s="4" t="inlineStr">
+      <c r="J112" s="4" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="I112" s="4" t="inlineStr">
+      <c r="K112" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J112" s="4" t="inlineStr">
+      <c r="L112" s="4" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -6082,20 +7184,30 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H113" s="8" t="inlineStr">
+      <c r="J113" s="8" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="K113" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J113" s="5" t="inlineStr">
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -6132,20 +7244,30 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr">
+      <c r="J114" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I114" s="4" t="inlineStr">
+      <c r="K114" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J114" s="4" t="inlineStr">
+      <c r="L114" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -6182,20 +7304,30 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr">
+      <c r="J115" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="K115" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J115" s="7" t="inlineStr">
+      <c r="L115" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -6232,20 +7364,30 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
+      <c r="J116" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I116" s="4" t="inlineStr">
+      <c r="K116" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J116" s="4" t="inlineStr">
+      <c r="L116" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -6282,20 +7424,30 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H117" s="8" t="inlineStr">
+      <c r="J117" s="8" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="K117" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J117" s="5" t="inlineStr">
+      <c r="L117" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -6332,20 +7484,30 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H118" s="4" t="inlineStr">
+      <c r="J118" s="4" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="I118" s="4" t="inlineStr">
+      <c r="K118" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J118" s="4" t="inlineStr">
+      <c r="L118" s="4" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -6382,20 +7544,30 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
           <t>球半</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="K119" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J119" s="5" t="inlineStr">
+      <c r="L119" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -6432,20 +7604,30 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H120" s="4" t="inlineStr">
+      <c r="J120" s="4" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="I120" s="4" t="inlineStr">
+      <c r="K120" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="J120" s="4" t="inlineStr">
+      <c r="L120" s="4" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -6482,20 +7664,30 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H121" s="8" t="inlineStr">
+      <c r="J121" s="8" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="K121" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J121" s="5" t="inlineStr">
+      <c r="L121" s="5" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
@@ -6532,20 +7724,30 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H122" s="4" t="inlineStr">
+      <c r="J122" s="4" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="I122" s="4" t="inlineStr">
+      <c r="K122" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J122" s="4" t="inlineStr">
+      <c r="L122" s="4" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -6582,20 +7784,30 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H123" s="5" t="inlineStr">
+      <c r="J123" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="I123" s="5" t="inlineStr">
+      <c r="K123" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J123" s="7" t="inlineStr">
+      <c r="L123" s="7" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -6632,20 +7844,30 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H124" s="4" t="inlineStr">
+      <c r="J124" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="I124" s="4" t="inlineStr">
+      <c r="K124" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J124" s="4" t="inlineStr">
+      <c r="L124" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -6682,20 +7904,30 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H125" s="8" t="inlineStr">
+      <c r="J125" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I125" s="5" t="inlineStr">
+      <c r="K125" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J125" s="5" t="inlineStr">
+      <c r="L125" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6732,20 +7964,30 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H126" s="4" t="inlineStr">
+      <c r="J126" s="4" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="I126" s="4" t="inlineStr">
+      <c r="K126" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J126" s="4" t="inlineStr">
+      <c r="L126" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -6782,20 +8024,30 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="J127" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="K127" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J127" s="7" t="inlineStr">
+      <c r="L127" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -6832,20 +8084,30 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H128" s="4" t="inlineStr">
+      <c r="J128" s="4" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I128" s="4" t="inlineStr">
+      <c r="K128" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="J128" s="4" t="inlineStr">
+      <c r="L128" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -6882,20 +8144,30 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H129" s="7" t="inlineStr">
+      <c r="J129" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="I129" s="5" t="inlineStr">
+      <c r="K129" s="5" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="J129" s="7" t="inlineStr">
+      <c r="L129" s="7" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -6932,20 +8204,30 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
           <t>球半</t>
         </is>
       </c>
-      <c r="H130" s="4" t="inlineStr">
+      <c r="J130" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="I130" s="4" t="inlineStr">
+      <c r="K130" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J130" s="4" t="inlineStr">
+      <c r="L130" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -6982,20 +8264,30 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H131" s="7" t="inlineStr">
+      <c r="J131" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
+      <c r="K131" s="5" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J131" s="7" t="inlineStr">
+      <c r="L131" s="7" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -7032,20 +8324,30 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H132" s="4" t="inlineStr">
+      <c r="J132" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="I132" s="4" t="inlineStr">
+      <c r="K132" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="J132" s="4" t="inlineStr">
+      <c r="L132" s="4" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -7082,20 +8384,30 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H133" s="7" t="inlineStr">
+      <c r="J133" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="K133" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J133" s="5" t="inlineStr">
+      <c r="L133" s="5" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -7132,20 +8444,30 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H134" s="4" t="inlineStr">
+      <c r="J134" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I134" s="4" t="inlineStr">
+      <c r="K134" s="4" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J134" s="4" t="inlineStr">
+      <c r="L134" s="4" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -7182,20 +8504,30 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H135" s="7" t="inlineStr">
+      <c r="J135" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
+      <c r="K135" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J135" s="5" t="inlineStr">
+      <c r="L135" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -7232,20 +8564,30 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
+      <c r="J136" s="4" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I136" s="4" t="inlineStr">
+      <c r="K136" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J136" s="4" t="inlineStr">
+      <c r="L136" s="4" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -7282,20 +8624,30 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H137" s="5" t="inlineStr">
+      <c r="J137" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I137" s="5" t="inlineStr">
+      <c r="K137" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="J137" s="7" t="inlineStr">
+      <c r="L137" s="7" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -7332,20 +8684,30 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H138" s="4" t="inlineStr">
+      <c r="J138" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I138" s="4" t="inlineStr">
+      <c r="K138" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J138" s="4" t="inlineStr">
+      <c r="L138" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7382,20 +8744,30 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H139" s="8" t="inlineStr">
+      <c r="J139" s="8" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="I139" s="5" t="inlineStr">
+      <c r="K139" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J139" s="5" t="inlineStr">
+      <c r="L139" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -7432,20 +8804,30 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H140" s="4" t="inlineStr">
+      <c r="J140" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I140" s="4" t="inlineStr">
+      <c r="K140" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J140" s="4" t="inlineStr">
+      <c r="L140" s="4" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -7482,20 +8864,30 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H141" s="5" t="inlineStr">
+      <c r="J141" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I141" s="5" t="inlineStr">
+      <c r="K141" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J141" s="8" t="inlineStr">
+      <c r="L141" s="8" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -7532,20 +8924,30 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
           <t>受球半</t>
         </is>
       </c>
-      <c r="H142" s="4" t="inlineStr">
+      <c r="J142" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I142" s="4" t="inlineStr">
+      <c r="K142" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J142" s="4" t="inlineStr">
+      <c r="L142" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7582,20 +8984,30 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H143" s="8" t="inlineStr">
+      <c r="J143" s="8" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
       </c>
-      <c r="I143" s="5" t="inlineStr">
+      <c r="K143" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J143" s="5" t="inlineStr">
+      <c r="L143" s="5" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -7632,20 +9044,30 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H144" s="4" t="inlineStr">
+      <c r="J144" s="4" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="I144" s="4" t="inlineStr">
+      <c r="K144" s="4" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="J144" s="4" t="inlineStr">
+      <c r="L144" s="4" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -7682,20 +9104,30 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H145" s="8" t="inlineStr">
+      <c r="J145" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I145" s="5" t="inlineStr">
+      <c r="K145" s="5" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="J145" s="5" t="inlineStr">
+      <c r="L145" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -7732,20 +9164,30 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr">
+      <c r="J146" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I146" s="4" t="inlineStr">
+      <c r="K146" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J146" s="4" t="inlineStr">
+      <c r="L146" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -7782,20 +9224,30 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H147" s="5" t="inlineStr">
+      <c r="J147" s="5" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="I147" s="5" t="inlineStr">
+      <c r="K147" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J147" s="7" t="inlineStr">
+      <c r="L147" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -7832,20 +9284,30 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H148" s="4" t="inlineStr">
+      <c r="J148" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I148" s="4" t="inlineStr">
+      <c r="K148" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J148" s="4" t="inlineStr">
+      <c r="L148" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -7882,20 +9344,30 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H149" s="7" t="inlineStr">
+      <c r="J149" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I149" s="5" t="inlineStr">
+      <c r="K149" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J149" s="7" t="inlineStr">
+      <c r="L149" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -7932,20 +9404,30 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
+          <t>2:6</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H150" s="4" t="inlineStr">
+      <c r="J150" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I150" s="4" t="inlineStr">
+      <c r="K150" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J150" s="4" t="inlineStr">
+      <c r="L150" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -7982,20 +9464,30 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H151" s="7" t="inlineStr">
+      <c r="J151" s="7" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
       </c>
-      <c r="I151" s="5" t="inlineStr">
+      <c r="K151" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="J151" s="5" t="inlineStr">
+      <c r="L151" s="5" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -8032,20 +9524,30 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H152" s="4" t="inlineStr">
+      <c r="J152" s="4" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="I152" s="4" t="inlineStr">
+      <c r="K152" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J152" s="4" t="inlineStr">
+      <c r="L152" s="4" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -8082,20 +9584,30 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
           <t>球半</t>
         </is>
       </c>
-      <c r="H153" s="7" t="inlineStr">
+      <c r="J153" s="7" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I153" s="5" t="inlineStr">
+      <c r="K153" s="5" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="J153" s="8" t="inlineStr">
+      <c r="L153" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -8132,20 +9644,30 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H154" s="4" t="inlineStr">
+      <c r="J154" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I154" s="4" t="inlineStr">
+      <c r="K154" s="4" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="J154" s="4" t="inlineStr">
+      <c r="L154" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -8182,20 +9704,30 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H155" s="7" t="inlineStr">
+      <c r="J155" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I155" s="5" t="inlineStr">
+      <c r="K155" s="5" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="J155" s="7" t="inlineStr">
+      <c r="L155" s="7" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -8232,20 +9764,30 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
           <t>受一球</t>
         </is>
       </c>
-      <c r="H156" s="4" t="inlineStr">
+      <c r="J156" s="4" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="I156" s="4" t="inlineStr">
+      <c r="K156" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J156" s="4" t="inlineStr">
+      <c r="L156" s="4" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -8282,20 +9824,30 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H157" s="7" t="inlineStr">
+      <c r="J157" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I157" s="5" t="inlineStr">
+      <c r="K157" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J157" s="5" t="inlineStr">
+      <c r="L157" s="5" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -8332,20 +9884,30 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H158" s="4" t="inlineStr">
+      <c r="J158" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I158" s="4" t="inlineStr">
+      <c r="K158" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J158" s="4" t="inlineStr">
+      <c r="L158" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -8382,20 +9944,30 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H159" s="7" t="inlineStr">
+      <c r="J159" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I159" s="7" t="inlineStr">
+      <c r="K159" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J159" s="5" t="inlineStr">
+      <c r="L159" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -8432,20 +10004,30 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H160" s="4" t="inlineStr">
+      <c r="J160" s="4" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
       </c>
-      <c r="I160" s="4" t="inlineStr">
+      <c r="K160" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J160" s="4" t="inlineStr">
+      <c r="L160" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -8482,20 +10064,30 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H161" s="5" t="inlineStr">
+      <c r="J161" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I161" s="5" t="inlineStr">
+      <c r="K161" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J161" s="5" t="inlineStr">
+      <c r="L161" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8532,20 +10124,30 @@
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="H162" s="4" t="inlineStr">
+      <c r="J162" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I162" s="4" t="inlineStr">
+      <c r="K162" s="4" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J162" s="4" t="inlineStr">
+      <c r="L162" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -8582,20 +10184,30 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H163" s="7" t="inlineStr">
+      <c r="J163" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="K163" s="5" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="J163" s="7" t="inlineStr">
+      <c r="L163" s="7" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -8632,20 +10244,30 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H164" s="4" t="inlineStr">
+      <c r="J164" s="4" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="I164" s="4" t="inlineStr">
+      <c r="K164" s="4" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="J164" s="4" t="inlineStr">
+      <c r="L164" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -8682,20 +10304,30 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H165" s="7" t="inlineStr">
+      <c r="J165" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I165" s="5" t="inlineStr">
+      <c r="K165" s="5" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="J165" s="7" t="inlineStr">
+      <c r="L165" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -8732,20 +10364,30 @@
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H166" s="4" t="inlineStr">
+      <c r="J166" s="4" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="I166" s="4" t="inlineStr">
+      <c r="K166" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J166" s="4" t="inlineStr">
+      <c r="L166" s="4" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -8782,20 +10424,30 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H167" s="8" t="inlineStr">
+      <c r="J167" s="8" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="I167" s="5" t="inlineStr">
+      <c r="K167" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J167" s="5" t="inlineStr">
+      <c r="L167" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -8832,20 +10484,30 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H168" s="4" t="inlineStr">
+      <c r="J168" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I168" s="4" t="inlineStr">
+      <c r="K168" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J168" s="4" t="inlineStr">
+      <c r="L168" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -8882,20 +10544,30 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H169" s="5" t="inlineStr">
+      <c r="J169" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I169" s="5" t="inlineStr">
+      <c r="K169" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J169" s="7" t="inlineStr">
+      <c r="L169" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8932,20 +10604,30 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H170" s="4" t="inlineStr">
+      <c r="J170" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I170" s="4" t="inlineStr">
+      <c r="K170" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J170" s="4" t="inlineStr">
+      <c r="L170" s="4" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
@@ -8982,20 +10664,30 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H171" s="8" t="inlineStr">
+      <c r="J171" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I171" s="5" t="inlineStr">
+      <c r="K171" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="J171" s="5" t="inlineStr">
+      <c r="L171" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -9032,20 +10724,30 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H172" s="4" t="inlineStr">
+      <c r="J172" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I172" s="4" t="inlineStr">
+      <c r="K172" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="J172" s="4" t="inlineStr">
+      <c r="L172" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -9082,20 +10784,30 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H173" s="7" t="inlineStr">
+      <c r="J173" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I173" s="5" t="inlineStr">
+      <c r="K173" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J173" s="5" t="inlineStr">
+      <c r="L173" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -9132,20 +10844,30 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
           <t>球半/两球</t>
         </is>
       </c>
-      <c r="H174" s="4" t="inlineStr">
+      <c r="J174" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I174" s="4" t="inlineStr">
+      <c r="K174" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J174" s="4" t="inlineStr">
+      <c r="L174" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9182,20 +10904,30 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H175" s="5" t="inlineStr">
+      <c r="J175" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="I175" s="5" t="inlineStr">
+      <c r="K175" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J175" s="8" t="inlineStr">
+      <c r="L175" s="8" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
@@ -9232,20 +10964,30 @@
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H176" s="4" t="inlineStr">
+      <c r="J176" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I176" s="4" t="inlineStr">
+      <c r="K176" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="J176" s="4" t="inlineStr">
+      <c r="L176" s="4" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -9282,20 +11024,30 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H177" s="5" t="inlineStr">
+      <c r="J177" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I177" s="5" t="inlineStr">
+      <c r="K177" s="5" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="J177" s="7" t="inlineStr">
+      <c r="L177" s="7" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -9332,20 +11084,30 @@
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H178" s="4" t="inlineStr">
+      <c r="J178" s="4" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="I178" s="4" t="inlineStr">
+      <c r="K178" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J178" s="4" t="inlineStr">
+      <c r="L178" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -9382,20 +11144,30 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H179" s="8" t="inlineStr">
+      <c r="J179" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I179" s="7" t="inlineStr">
+      <c r="K179" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="J179" s="5" t="inlineStr">
+      <c r="L179" s="5" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -9432,20 +11204,30 @@
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H180" s="4" t="inlineStr">
+      <c r="J180" s="4" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="I180" s="4" t="inlineStr">
+      <c r="K180" s="4" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="J180" s="4" t="inlineStr">
+      <c r="L180" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9482,20 +11264,30 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H181" s="8" t="inlineStr">
+      <c r="J181" s="8" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="I181" s="5" t="inlineStr">
+      <c r="K181" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J181" s="5" t="inlineStr">
+      <c r="L181" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -9532,20 +11324,30 @@
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H182" s="4" t="inlineStr">
+      <c r="J182" s="4" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="I182" s="4" t="inlineStr">
+      <c r="K182" s="4" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="J182" s="4" t="inlineStr">
+      <c r="L182" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9582,20 +11384,26 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr"/>
+      <c r="I183" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="J183" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
+      <c r="K183" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J183" s="8" t="inlineStr">
+      <c r="L183" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -9632,20 +11440,26 @@
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr"/>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H184" s="4" t="inlineStr">
+      <c r="J184" s="4" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="I184" s="4" t="inlineStr">
+      <c r="K184" s="4" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="J184" s="4" t="inlineStr">
+      <c r="L184" s="4" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -9682,20 +11496,26 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr"/>
+      <c r="I185" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H185" s="7" t="inlineStr">
+      <c r="J185" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
+      <c r="K185" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J185" s="7" t="inlineStr">
+      <c r="L185" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
@@ -9732,20 +11552,26 @@
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr"/>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H186" s="4" t="inlineStr">
+      <c r="J186" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="I186" s="4" t="inlineStr">
+      <c r="K186" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J186" s="4" t="inlineStr">
+      <c r="L186" s="4" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -9782,20 +11608,26 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr"/>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H187" s="7" t="inlineStr">
+      <c r="J187" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="K187" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J187" s="7" t="inlineStr">
+      <c r="L187" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
@@ -9832,20 +11664,26 @@
       </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr"/>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H188" s="4" t="inlineStr">
+      <c r="J188" s="4" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="I188" s="4" t="inlineStr">
+      <c r="K188" s="4" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="J188" s="4" t="inlineStr">
+      <c r="L188" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -9882,20 +11720,26 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr"/>
+      <c r="I189" s="5" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="J189" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="I189" s="8" t="inlineStr">
+      <c r="K189" s="8" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="J189" s="5" t="inlineStr">
+      <c r="L189" s="5" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -9932,20 +11776,26 @@
       </c>
       <c r="G190" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="inlineStr"/>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H190" s="4" t="inlineStr">
+      <c r="J190" s="4" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="I190" s="4" t="inlineStr">
+      <c r="K190" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J190" s="4" t="inlineStr">
+      <c r="L190" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -9982,20 +11832,26 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr"/>
+      <c r="I191" s="5" t="inlineStr">
+        <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H191" s="8" t="inlineStr">
+      <c r="J191" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I191" s="5" t="inlineStr">
+      <c r="K191" s="5" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="J191" s="5" t="inlineStr">
+      <c r="L191" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -10032,20 +11888,26 @@
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr"/>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
           <t>受一球/球半</t>
         </is>
       </c>
-      <c r="H192" s="4" t="inlineStr">
+      <c r="J192" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="I192" s="4" t="inlineStr">
+      <c r="K192" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J192" s="4" t="inlineStr">
+      <c r="L192" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -10082,20 +11944,26 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr"/>
+      <c r="I193" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H193" s="7" t="inlineStr">
+      <c r="J193" s="7" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="I193" s="5" t="inlineStr">
+      <c r="K193" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J193" s="5" t="inlineStr">
+      <c r="L193" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -10132,20 +12000,26 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr"/>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H194" s="4" t="inlineStr">
+      <c r="J194" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I194" s="4" t="inlineStr">
+      <c r="K194" s="4" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J194" s="4" t="inlineStr">
+      <c r="L194" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -10182,20 +12056,26 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr"/>
+      <c r="I195" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H195" s="5" t="inlineStr">
+      <c r="J195" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I195" s="8" t="inlineStr">
+      <c r="K195" s="8" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J195" s="5" t="inlineStr">
+      <c r="L195" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10232,20 +12112,26 @@
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr"/>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H196" s="4" t="inlineStr">
+      <c r="J196" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I196" s="4" t="inlineStr">
+      <c r="K196" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="J196" s="4" t="inlineStr">
+      <c r="L196" s="4" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
@@ -10282,20 +12168,26 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr"/>
+      <c r="I197" s="5" t="inlineStr">
+        <is>
           <t>两球</t>
         </is>
       </c>
-      <c r="H197" s="8" t="inlineStr">
+      <c r="J197" s="8" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="I197" s="5" t="inlineStr">
+      <c r="K197" s="5" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="J197" s="5" t="inlineStr">
+      <c r="L197" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -10332,20 +12224,26 @@
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr"/>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H198" s="4" t="inlineStr">
+      <c r="J198" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I198" s="4" t="inlineStr">
+      <c r="K198" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J198" s="4" t="inlineStr">
+      <c r="L198" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -10382,20 +12280,26 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr"/>
+      <c r="I199" s="5" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H199" s="5" t="inlineStr">
+      <c r="J199" s="5" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="I199" s="5" t="inlineStr">
+      <c r="K199" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J199" s="8" t="inlineStr">
+      <c r="L199" s="8" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -10432,20 +12336,26 @@
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr"/>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H200" s="4" t="inlineStr">
+      <c r="J200" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I200" s="4" t="inlineStr">
+      <c r="K200" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J200" s="4" t="inlineStr">
+      <c r="L200" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -10482,20 +12392,26 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr"/>
+      <c r="I201" s="5" t="inlineStr">
+        <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H201" s="7" t="inlineStr">
+      <c r="J201" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I201" s="7" t="inlineStr">
+      <c r="K201" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J201" s="5" t="inlineStr">
+      <c r="L201" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -10532,20 +12448,26 @@
       </c>
       <c r="G202" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr"/>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H202" s="4" t="inlineStr">
+      <c r="J202" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I202" s="4" t="inlineStr">
+      <c r="K202" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J202" s="4" t="inlineStr">
+      <c r="L202" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -10582,20 +12504,26 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr"/>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H203" s="8" t="inlineStr">
+      <c r="J203" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I203" s="7" t="inlineStr">
+      <c r="K203" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="J203" s="5" t="inlineStr">
+      <c r="L203" s="5" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -10632,20 +12560,26 @@
       </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" s="4" t="inlineStr"/>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H204" s="4" t="inlineStr">
+      <c r="J204" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I204" s="4" t="inlineStr">
+      <c r="K204" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J204" s="4" t="inlineStr">
+      <c r="L204" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -10682,20 +12616,26 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr"/>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H205" s="8" t="inlineStr">
+      <c r="J205" s="8" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="I205" s="5" t="inlineStr">
+      <c r="K205" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J205" s="5" t="inlineStr">
+      <c r="L205" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -10765,9 +12705,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
